--- a/Checklists/HLR_review_checklist.xlsx
+++ b/Checklists/HLR_review_checklist.xlsx
@@ -44,9 +44,6 @@
 but it should not be detailed.</t>
   </si>
   <si>
-    <t>We can use a graphical representation for better understanding and all the naming should be clear as per guideline. (ex- variable start with _ or alphabet and macro in capital letter always etc).</t>
-  </si>
-  <si>
     <t>HLR should be properly divided as per application.</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t xml:space="preserve">While writing HLR version should be mentioned so later if any changes then we can update. </t>
+  </si>
+  <si>
+    <t>We can use a graphical representation for better understanding and all the naming should be clear as per guideline. (ex. variable start with _ or alphabet and macro in capital letter always etc).</t>
   </si>
 </sst>
 </file>
@@ -461,7 +461,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8">
@@ -477,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8">
@@ -485,7 +485,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8">
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -501,7 +501,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="8:8">
